--- a/important_mails_2026-04-27.xlsx
+++ b/important_mails_2026-04-27.xlsx
@@ -1296,7 +1296,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1311,187 +1311,21 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
+          <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0DD7R3PPG" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
-1. Go to the Account Health page and select the Regulatory Compliance tab
-2. Choose next steps.
-3. Click Submit button for the product y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
- DOC REVIEW</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-● The document uploaded for "B0FCDRNTT8x`" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
-The SDS does not include the legislation/regulation in accordance with the document was created
-Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
-For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
-Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
-1. Go to the Account Health page and select the Regulatory Compliance tab
-2. Choose next steps.
-3. Click Submit button for the product</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon DV TIC</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的卖家，您好。
-我们可以为您提供亚马逊DV验证报告服务。
-验证费用：
-【玩具】500元（RMB）/ASIN；
-【电动自行车用充电器及电池】4500元（RMB）/ASIN；
-【移动电源及便携式电源产品】5000元（RMB）/ASIN。
-如涉及较多ASIN或有其他需求，我们将根据具体情况提供优惠报价。
-商品测试：
-如您的商品需额外进行合规测试，请提供实物图片和商品参数以及销售国家等，以便评估测试费用。
-服务流程如下：
-登录卖家中心 “合规管理”（MYC）；
-针对待处理 ASIN，选择 “CVC威凯” 提交验证申请；
-提供所需资料：申请表、测试报告、产品六面实物照片（非包装图）、标签警示语、用户手册/使用说明书等；
-CVC威凯将进行检测或合规验证，并将结果直接提交亚马逊；如需整改，我们会及时与您沟通。
-如需进一步了解或希望直接安排服务，可直接通过以下方式联系我，我们将全程协助您完成验证流程。
-您也可联系官方邮箱专员咨询：amazondv@cei1958.com
-感谢您的支持，期待与您合作！
-如您已经对接我司业务员，请忽略此信息，不便之处敬请谅解。
-Dear Seller,
-Greetings.
-We are pleased to offer Amazon DV Verification Report services to support your compliance needs.
-Verification Fee:
-【Toys】¥500 (RMB) per ASIN.
-【E-bikes lithium-ion batteries and chargers】¥4500 (RMB) per ASIN.
-【Power Bank and Portable Power Station】¥5000 (RMB) per ASIN.
-If you have multiple ASINs or special requirements, we can provide a customized discounted quote based on your situation.
-Product Testing:If your product requires additional compliance testing, please provide physical product photos, specify the target sales country/region and product parameter so we can assess the testing fees accordingly.
-Service Process:
-Log in to your Seller Central and navigate to “Compliance Managemen</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1507,39 +1341,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1560,39 +1394,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -1610,40 +1444,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -1661,39 +1495,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1710,39 +1544,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -1760,40 +1594,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1811,39 +1645,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -1861,39 +1695,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1910,39 +1744,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1957,39 +1791,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2008,39 +1842,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -2058,39 +1892,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -2129,39 +1963,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2177,40 +2011,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2226,39 +2060,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2274,39 +2108,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2320,40 +2154,40 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2369,39 +2203,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2417,39 +2251,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2473,39 +2307,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2526,39 +2360,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2574,39 +2408,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2626,39 +2460,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2684,39 +2518,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2737,39 +2571,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2795,39 +2629,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2847,39 +2681,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2895,39 +2729,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2947,39 +2781,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2996,39 +2830,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -3040,39 +2874,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3095,39 +2929,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3151,39 +2985,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3198,39 +3032,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3244,40 +3078,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3294,39 +3128,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3346,39 +3180,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3395,39 +3229,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3450,39 +3284,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3499,6 +3333,172 @@
 Thank you for selling in the Amazon store,
 Amazon Services
 Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 14:16:35 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
+ A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0DD7R3PPG" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
+1. Go to the Account Health page and select the Regulatory Compliance tab
+2. Choose next steps.
+3. Click Submit button for the product y</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 09:57:17 +0000</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
+ DOC REVIEW</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+● The document uploaded for "B0FCDRNTT8x`" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS must be composed in accordance with a valid regulation/legislation for Chemical Safety Compliance( for which your product is listed and stored ).
+The SDS does not include the legislation/regulation in accordance with the document was created
+Legislation/regulation should be also mentioned in section 2 “Hazard Identification”.
+For guidance on Safety Data Sheet requirements, please refer to https://sellercentral.amazon.com/help/hub/reference/G5G6BBSA6FZQP9CP
+Once you have corrected the problems listed above, please re-upload a valid document in Account Health Dashboard under "Regulatory Compliance" section. For any questions/appeals regarding these product/other products, please submit them ( for each ASIN separately ) in "Account Health Dashboard" under the relevant Appeal reason:
+1. Go to the Account Health page and select the Regulatory Compliance tab
+2. Choose next steps.
+3. Click Submit button for the product</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 16:06:35 +0800 (GMT+08:00)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Amazon DV TIC</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家，您好。
+我们可以为您提供亚马逊DV验证报告服务。
+验证费用：
+【玩具】500元（RMB）/ASIN；
+【电动自行车用充电器及电池】4500元（RMB）/ASIN；
+【移动电源及便携式电源产品】5000元（RMB）/ASIN。
+如涉及较多ASIN或有其他需求，我们将根据具体情况提供优惠报价。
+商品测试：
+如您的商品需额外进行合规测试，请提供实物图片和商品参数以及销售国家等，以便评估测试费用。
+服务流程如下：
+登录卖家中心 “合规管理”（MYC）；
+针对待处理 ASIN，选择 “CVC威凯” 提交验证申请；
+提供所需资料：申请表、测试报告、产品六面实物照片（非包装图）、标签警示语、用户手册/使用说明书等；
+CVC威凯将进行检测或合规验证，并将结果直接提交亚马逊；如需整改，我们会及时与您沟通。
+如需进一步了解或希望直接安排服务，可直接通过以下方式联系我，我们将全程协助您完成验证流程。
+您也可联系官方邮箱专员咨询：amazondv@cei1958.com
+感谢您的支持，期待与您合作！
+如您已经对接我司业务员，请忽略此信息，不便之处敬请谅解。
+Dear Seller,
+Greetings.
+We are pleased to offer Amazon DV Verification Report services to support your compliance needs.
+Verification Fee:
+【Toys】¥500 (RMB) per ASIN.
+【E-bikes lithium-ion batteries and chargers】¥4500 (RMB) per ASIN.
+【Power Bank and Portable Power Station】¥5000 (RMB) per ASIN.
+If you have multiple ASINs or special requirements, we can provide a customized discounted quote based on your situation.
+Product Testing:If your product requires additional compliance testing, please provide physical product photos, specify the target sales country/region and product parameter so we can assess the testing fees accordingly.
+Service Process:
+Log in to your Seller Central and navigate to “Compliance Managemen</t>
         </is>
       </c>
     </row>

--- a/important_mails_2026-04-27.xlsx
+++ b/important_mails_2026-04-27.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1246,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1261,71 +1261,21 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
+          <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -1341,39 +1291,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -1394,39 +1344,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -1444,40 +1394,40 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -1495,39 +1445,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -1544,39 +1494,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -1594,40 +1544,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -1645,39 +1595,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -1695,39 +1645,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1744,39 +1694,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1791,39 +1741,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1842,39 +1792,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -1892,39 +1842,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -1963,39 +1913,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2011,40 +1961,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2060,39 +2010,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2108,39 +2058,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -2154,40 +2104,40 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2203,39 +2153,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2251,39 +2201,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2307,39 +2257,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2360,39 +2310,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:54:23 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $44.85 in an attempt to settle your Amazon seller account balance.
@@ -2408,39 +2358,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 04:59:05 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (26041219YV)</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2460,39 +2410,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (W4mGNrNTVu)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2518,39 +2468,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2571,39 +2521,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -2629,39 +2579,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2681,39 +2631,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:45:45 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -2729,39 +2679,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Apr 2026 14:44:32 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2781,39 +2731,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:38:30 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2830,39 +2780,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 16:26:54 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;amazon_te@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Paiement du solde de votre compte de paiement Vendre sur Amazon</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Cher vendeur,
  Nous avons débité votre carte bancaire (Visa) pour un montant de 242,36 EUR pour le règlement du solde de votre compte de paiement Vendre sur Amazon.
@@ -2874,39 +2824,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Apr 2026 15:24:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Negative balance adjustment across your Selling on Amazon accounts</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2929,39 +2879,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Apr 2026 15:29:23 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2985,39 +2935,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 14:28:35 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 62.05 in an attempt to settle your account balance.
@@ -3032,39 +2982,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 15:16:38 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 45.29. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -3078,40 +3028,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Refunds for digital services fees related to the Canadian DST will
  begin on April 15</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
@@ -3128,39 +3078,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3180,39 +3130,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3229,39 +3179,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -3284,39 +3234,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3333,6 +3283,56 @@
 Thank you for selling in the Amazon store,
 Amazon Services
 Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 20 Apr 2026 21:09:24 +0000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4431,121 +4431,21 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
+          <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4566,39 +4466,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4613,39 +4513,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Verify your primary operating address for tax purposes</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  Verify your primary operating address for tax purposes
@@ -4662,39 +4562,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 15:10:49 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>[Formal Notice – Immediate Action Required] Review and certify your business information within 10 days to avoid account deactivation</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4708,39 +4608,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:59:02 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Verkaeuferservice &lt;merch.service05@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12354633592] 其他账户问题</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>尊敬的销售伙伴：
 您好！
@@ -4759,40 +4659,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 17:22:14 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Product Support Team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Reduce Returns &amp; Boost Customer Satisfaction - Enrol in Amazon
  Product Support</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Enrol now into Amazon Product Support !
@@ -4806,40 +4706,40 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 13:44:27 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Reactiva tus listings en la UE: se requiere el cumplimiento del
  Reglamento relativo a la seguridad general de los productos</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Reactiva tus listings en la UE: se requiere el cumplimiento del Reglamento relativo a la seguridad general de los productos
@@ -4857,39 +4757,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 01:52:13 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 Just a short follow-up regarding the [Vergleich.org](http://Vergleich.org)
@@ -4922,39 +4822,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 17:17:52 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Introducing Global Warehousing &amp; Distribution</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Store inventory at origin in China with lower costs and faster speeds.
@@ -4969,39 +4869,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 16:27:24 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 3/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5020,39 +4920,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:49:51 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Riattivare le offerte nell'UE - Richiesta la conformità al Regolamento sulla sicurezza generale dei prodotti
@@ -5071,39 +4971,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:53:45 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Las tarifas por puesta de inventario a disposición de Amazon y retirada de Logística de Amazon se cobrarán a medida que se procesen las unidades</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Las tarifas por retirada y puesta de inventario a disposición de Amazon de Logística de Amazon se cobrarán ahora por unidad en el momento en que cada unidad se retire o se ponga a nuestra disposición.
@@ -5115,39 +5015,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 09:19:33 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Opłaty za usunięcie i likwidację zapasów FBA naliczane podczas przetwarzania jednostek</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Opłaty za wycofanie i usunięcie zapasów w ramach FBA będą teraz pobierane od każdej jednostki w momencie jej wycofania lub usunięcia.
@@ -5163,39 +5063,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 08:46:52 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Addebito delle tariffe di rimozione e per reimpiego quando le unità vengono elaborate</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Le tariffe per gli ordini di rimozione e di reimpiego di inventario di Logistica di Amazon verranno ora addebitate per unità ogni volta che un'unità viene rimossa o destinata ad altro uso.
@@ -5207,39 +5107,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 8 Apr 2026 15:00:43 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5254,39 +5154,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 01:13:24 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5298,39 +5198,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 00:28:23 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5342,39 +5242,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5386,39 +5286,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5430,39 +5330,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5474,39 +5374,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5518,39 +5418,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5562,39 +5462,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5606,39 +5506,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5650,39 +5550,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5701,39 +5601,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5745,39 +5645,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5789,39 +5689,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5833,39 +5733,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5877,39 +5777,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -5921,39 +5821,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -5965,39 +5865,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6009,39 +5909,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6060,39 +5960,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6104,40 +6004,40 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -6156,39 +6056,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6200,39 +6100,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -6251,39 +6151,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -6315,39 +6215,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -6374,39 +6274,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -6418,39 +6318,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -6460,39 +6360,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -6502,39 +6402,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -6564,39 +6464,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -6614,39 +6514,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -6663,39 +6563,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -6711,39 +6611,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -6772,39 +6672,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -6825,86 +6725,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulazioni. Il pagamento è stato elaborato con successo e ti sarà accreditato a breve.
- Tentativo di pagamento
-Congratulazioni Weihai EU! Il pagamento è stato elaborato con successo e ti sarà accreditato nel giro di da tre a cinque giorni.
-In data 03/28/26 15:19 CET, abbiamo avviato un trasferimento sul tuo metodo di pagamento (conto bancario che termina con 229) dell’importo di €
- 217,83.
- Se l’importo è inferiore a quanto atteso, tieni in considerazione le seguenti domande:
- Hai un saldo non disponibile? Amazon potrebbe trattenere una certa somma per coprire i costi di eventuali resi, reclami o contestazioni di una transazione (chargeback) da parte degli acquirenti. In questo caso, il saldo finale nel tuo report sui pagamenti mostrerà il saldo non disponibile corrispondente alla cifra trattenuta.
- Le tue vendite coprono tutte le commissioni e i resi per questo ciclo di fatturazione? L’importo del pagamento rispecchia le attività di vendita, le commissioni di vendita e le tariffe per promozioni o servizi. Ti consigliamo di rivedere il report sui pagamenti nella scheda Report di Seller Central per comprendere le diverse spese che p</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6926,39 +6779,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6981,39 +6834,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:58:06 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-23</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7034,39 +6887,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Apr 2026 18:27:29 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7089,39 +6942,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
@@ -7134,39 +6987,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -7175,39 +7028,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7223,39 +7076,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Apr 2026 14:20:37 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Get discounts up to €500 per shipment by expanding to Europe!</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/-logo/7z2qvdy/6598918207/h/oQJ3hcZAc232rnIjbHrMLH2dvtBVfEq_dAzSA60S8Es)
 C2S2 PCP Pallet Limited Time Promotion
@@ -7271,39 +7124,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 11:27:28 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time each unit is removed or disposed of.
@@ -7323,39 +7176,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Apr 2026 10:52:42 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>FBA removal and disposal fees to be charged as units are processed</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  FBA removal and disposal fees will now be charged on a per-unit basis at the time that each unit is removed or disposed of.
@@ -7374,39 +7227,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 7 Apr 2026 09:23:39 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Update to FBA item package dimensions
  96
@@ -7415,39 +7268,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -7465,39 +7318,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -7527,54 +7380,6 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] – Update Inventory -FBA</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
-We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
-https://sellercentral.amazon.ca/restockinventory/recommendations
-Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
-B0DMFL5X12, B0D7QHCF8J
-You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
-For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this report to the correct point of contact.
-If you wish to unsubscribe please REPLY ALL with the subject l</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
